--- a/artfynd/A 40235-2022 artfynd.xlsx
+++ b/artfynd/A 40235-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120260059</v>
       </c>
       <c r="B2" t="n">
-        <v>91825</v>
+        <v>91843</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>120260056</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>91876</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 40235-2022 artfynd.xlsx
+++ b/artfynd/A 40235-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120260059</v>
+        <v>120260056</v>
       </c>
       <c r="B2" t="n">
-        <v>91843</v>
+        <v>91876</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1968</v>
+        <v>4368</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>382941</v>
+        <v>382945</v>
       </c>
       <c r="R2" t="n">
-        <v>6657945</v>
+        <v>6657952</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120260056</v>
+        <v>120260059</v>
       </c>
       <c r="B3" t="n">
-        <v>91876</v>
+        <v>91843</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4368</v>
+        <v>1968</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>382945</v>
+        <v>382941</v>
       </c>
       <c r="R3" t="n">
-        <v>6657952</v>
+        <v>6657945</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 40235-2022 artfynd.xlsx
+++ b/artfynd/A 40235-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120260056</v>
+        <v>120260059</v>
       </c>
       <c r="B2" t="n">
-        <v>91876</v>
+        <v>91843</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4368</v>
+        <v>1968</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>382945</v>
+        <v>382941</v>
       </c>
       <c r="R2" t="n">
-        <v>6657952</v>
+        <v>6657945</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120260059</v>
+        <v>120260056</v>
       </c>
       <c r="B3" t="n">
-        <v>91843</v>
+        <v>91876</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1968</v>
+        <v>4368</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>382941</v>
+        <v>382945</v>
       </c>
       <c r="R3" t="n">
-        <v>6657945</v>
+        <v>6657952</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 40235-2022 artfynd.xlsx
+++ b/artfynd/A 40235-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>120260059</v>
       </c>
       <c r="B2" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,12 +787,7 @@
         <v>120260056</v>
       </c>
       <c r="B3" t="n">
-        <v>91924</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
